--- a/data/file_generation/reference/data_211/10月月考表彰名单_res.xlsx
+++ b/data/file_generation/reference/data_211/10月月考表彰名单_res.xlsx
@@ -1214,18 +1214,26 @@
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
+  <documentManagement>
+    <SharedWithUsers xmlns="eca6eae4-1627-4e8d-9a6b-5b4dd91506e7">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13944CDD-D9D9-44D9-B4F4-01AA931794FC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{52A07A25-D4FC-4DB7-AAA7-E157AD28CA37}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{928A5A8B-EB7F-47A4-9BC7-73086C78EFBF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{10101699-ADFD-4637-8C4F-261E04439678}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AFB45CF-AFD6-4323-86AA-4CC6CDB3E1D8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{52B308E3-79DF-4F73-83EE-82C84E43FDBD}"/>
 </file>